--- a/output/2026-09-19_17_Croazia_Osjecko-baranjska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-19_17_Croazia_Osjecko-baranjska_ATEX_Equipment-Services.xlsx
@@ -484,7 +484,6 @@
           <t>+385 31 307 933</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Distributore verificato: vende ventilatori elettrici ATEX (es. SAX350) e rilevatori di gas fissi/portatili con approvazione ATEX explosion proof (es. SI-100R). Fonte: sito ufficiale vatropromet.hr, sale center Osijek.</t>
@@ -522,10 +521,9 @@
           <t>031 251 155</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Azienda verificata, attiva dal 1998, pagina dedicata 'Protueksplozijska zastita (Ex)' sul sito con servizi di ispezione impianti elettrici in aree Ex, classificazione zone pericolose e manuali Ex. Email generica non reperita con certezza (dato omesso). Fonte: zus.hr, fininfo.hr, companywall.hr.</t>
+          <t>Azienda verificata, attiva dal 1998, pagina dedicata 'Protueksplozijska zastita (Ex)' sul sito con servizi di ispezione impianti elettrici in aree Ex, classificazione zone pericolose e manuali Ex. Email generica non reperita con certezza (dato omesso). Fonte: zus.hr, fininfo.hr, companywall.hr. [DUPLICATO — vedi anche: 2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -567,7 +565,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Azienda verificata, attiva dal 2000, pagina dedicata 'Protueksplozijska (Ex) zastita' con servizi di ispezione, valutazione rischio esplosione, misurazioni e redazione manuali Ex. Telefono ed email confermati da piu fonti indipendenti. Fonte: zastitainspekt.hr, fininfo.hr.</t>
+          <t>Azienda verificata, attiva dal 2000, pagina dedicata 'Protueksplozijska (Ex) zastita' con servizi di ispezione, valutazione rischio esplosione, misurazioni e redazione manuali Ex. Telefono ed email confermati da piu fonti indipendenti. Fonte: zastitainspekt.hr, fininfo.hr. [DUPLICATO — vedi anche: 2026-09-13_16_Croazia_Bjelovarsko-bilogorska_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">

--- a/output/2026-09-19_17_Croazia_Osjecko-baranjska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-19_17_Croazia_Osjecko-baranjska_ATEX_Equipment-Services.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (21/09/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-09-19_17_Croazia_Osjecko-baranjska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-19_17_Croazia_Osjecko-baranjska_ATEX_Equipment-Services.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Distributore verificato: vende ventilatori elettrici ATEX (es. SAX350) e rilevatori di gas fissi/portatili con approvazione ATEX explosion proof (es. SI-100R). Fonte: sito ufficiale vatropromet.hr, sale center Osijek.</t>
+          <t>Distributore verificato: vende ventilatori elettrici ATEX (es. SAX350) e rilevatori di gas fissi/portatili con approvazione ATEX explosion proof (es. SI-100R). Fonte: sito ufficiale vatropromet.hr, sale center Osijek. [DUPLICATO — vedi anche: 2026-09-07_22_Croazia_Zagrebacka_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
